--- a/www/download/IND.exchange.r.us.EXI382.xlsx
+++ b/www/download/IND.exchange.r.us.EXI382.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,487 +678,5887 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>AUS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1.1095</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>AUT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>1.308</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1.308</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>BEL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1.3009509202454</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.3009509202454</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.3009509202454</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1.3009509202454</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1.3009509202454</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1.3009509202454</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1.3009509202454</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1.3009509202454</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1.3009509202454</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1.3009509202454</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1.3009509202454</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.3009509202454</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1.3009509202454</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>1.3009509202454</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1.3009509202454</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1.3009509202454</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1.3009509202454</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1.3009509202454</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>1.3009509202454</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1.3009509202454</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>1.3009509202454</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1.3009509202454</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1.30071595092025</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>1.30071595092025</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1.30071595092025</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>1.30071595092025</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1.30071595092025</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>BGR</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1.2697</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>BRA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1.3281</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>CAN</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1.2848</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>CHN</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>1.37621595092025</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>1.37555828220859</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>1.37555828220859</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>1.37555828220859</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1.37555828220859</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>CYP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1.2197490797546</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.2197490797546</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.2197490797546</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1.2197490797546</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1.2197490797546</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1.2197490797546</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1.2197490797546</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1.2197490797546</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1.2197490797546</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1.2197490797546</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1.2197490797546</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1.2197490797546</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1.2197490797546</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1.2197490797546</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1.2197490797546</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1.2197490797546</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1.2197490797546</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1.21891656441718</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1.21891656441718</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1.21891656441718</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>1.21891656441718</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1.21891656441718</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>1.21891656441718</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>1.21891656441718</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>1.21891656441718</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>1.21891656441718</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1.21891656441718</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>CZE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>1.134</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1.134</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>DEU</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1.1268773006135</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.1268773006135</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.1268773006135</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1.1268773006135</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1.1268773006135</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1.1268773006135</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1.1268773006135</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1.1268773006135</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1.1268773006135</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1.1268773006135</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1.1268773006135</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1.1268773006135</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1.1267981595092</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1.1267981595092</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1.1267981595092</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1.1267981595092</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1.1267981595092</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1.1267981595092</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1.1267981595092</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1.1267981595092</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>1.1267981595092</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>1.1267981595092</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>1.1267981595092</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>1.1267981595092</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1.1267981595092</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>1.1267981595092</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1.1267981595092</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>DNK</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1.1211</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>ESP</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1.0658</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>EST</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1.08038834355828</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1.08038834355828</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.08038834355828</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1.08038834355828</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1.08038834355828</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1.08038834355828</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1.08038834355828</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1.0800490797546</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1.0800490797546</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1.0800490797546</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>1.0800490797546</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1.0800490797546</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1.0800490797546</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>1.0800490797546</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1.0800490797546</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1.0800490797546</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1.0800490797546</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1.0800490797546</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>1.0800490797546</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>1.0800490797546</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>1.0800490797546</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>1.0800490797546</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>1.0800490797546</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>1.0800490797546</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>1.0800490797546</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>1.0800490797546</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>1.0800490797546</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>FIN</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0.934941104294479</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0.934941104294479</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>0.934068711656442</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>FRA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>0.920507975460123</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>0.920336196319018</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>0.920336196319018</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>0.920336196319018</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>GBR</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1.34138527607362</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1.34138527607362</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.34138527607362</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1.34138527607362</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1.34138527607362</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1.34138527607362</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1.34096134969325</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1.34096134969325</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1.34096134969325</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1.34096134969325</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1.34096134969325</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1.34096134969325</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1.34096134969325</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>1.34096134969325</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1.34096134969325</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1.34096134969325</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1.34096134969325</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1.34096134969325</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>1.34096134969325</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1.34096134969325</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>1.34096134969325</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>1.34096134969325</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>1.34096134969325</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>1.34096134969325</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>1.34096134969325</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>1.34096134969325</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>1.34096134969325</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>GRC</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>0.8956</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>HUN</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>0.9456</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>IDN</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1.32830613496933</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1.32830613496933</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.32830613496933</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1.32830613496933</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1.32830613496933</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>1.32830613496933</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1.32830613496933</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1.32830613496933</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>1.32830613496933</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1.32830613496933</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>1.32830613496933</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>1.32830613496933</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>1.32830613496933</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>1.32830858895706</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1.32830858895706</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1.32830858895706</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1.32830858895706</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1.32830858895706</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>1.32830858895706</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>1.32830858895706</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>1.32830858895706</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>1.32830858895706</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>1.32830858895706</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>1.32830858895706</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>1.32830858895706</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>1.32830858895706</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>1.32830858895706</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>IND</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>1.181</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1.181</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>IRL</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1.03441472392638</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1.03441472392638</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.03441472392638</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1.03441472392638</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1.03441472392638</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1.03441472392638</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1.03441472392638</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1.03441472392638</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1.03441472392638</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1.03441472392638</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1.03441472392638</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1.03441472392638</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1.03441472392638</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>1.03441472392638</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1.03555337423313</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1.03555337423313</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1.03555337423313</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1.03555337423313</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1.03555337423313</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1.03555337423313</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>1.03555337423313</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>1.03555337423313</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>1.03555337423313</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>1.03555337423313</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>1.03555337423313</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>1.03555337423313</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1.03555337423313</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>ITA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1.1312</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>JPN</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1.3891527607362</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>1.38955950920245</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>KOR</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1.29914478527607</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1.29914478527607</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.29914478527607</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1.29914478527607</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1.29914478527607</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>1.29914478527607</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1.29914478527607</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1.29914478527607</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>1.29914478527607</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1.29914478527607</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>1.29914478527607</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>1.29914478527607</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>1.29914478527607</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>1.29914478527607</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1.29914478527607</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1.29914478527607</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1.29914478527607</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1.29914478527607</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>1.29941042944785</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>1.29941042944785</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>1.29941042944785</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>1.29941042944785</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>1.29941042944785</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>1.29941042944785</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>1.29941042944785</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>1.29941042944785</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>1.29941042944785</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>LTU</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1.20587239263804</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1.20587239263804</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.20587239263804</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1.20587239263804</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1.20587239263804</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>1.20587239263804</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1.20587239263804</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1.20587239263804</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>1.20587239263804</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1.20656380368098</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>1.20656380368098</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>1.20656380368098</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>1.20656380368098</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>1.20656380368098</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1.20656380368098</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1.20656380368098</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1.20656380368098</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1.20656380368098</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>1.20656380368098</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>1.20656380368098</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>1.20656380368098</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>1.20656380368098</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>1.20656380368098</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>1.20656380368098</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>1.20656380368098</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>1.20656380368098</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>1.20656380368098</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>LUX</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>1.2439</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>LVA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1.24406932515337</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1.24406932515337</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.24406932515337</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1.24406932515337</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>1.24407055214724</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>MEX</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>1.3285</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>MLT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>1.24452331288344</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>1.24459386503067</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>NLD</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>1.2556</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>POL</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1.28097668711656</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1.28097668711656</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.28097668711656</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1.28097668711656</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1.28097668711656</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>1.28097668711656</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1.28097668711656</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>1.28097668711656</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>1.28097668711656</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>1.28097668711656</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>1.28097668711656</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>1.28097668711656</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>1.28097668711656</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>1.28097668711656</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1.28097668711656</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1.28097668711656</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1.28097668711656</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1.28097668711656</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>1.28097668711656</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>1.28097668711656</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>1.28097668711656</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>1.28168159509202</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>1.28168159509202</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>1.28168159509202</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>1.28168159509202</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>1.28168159509202</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>1.28168159509202</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>PRT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>1.3705</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>ROU</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1.41111226993865</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1.41111226993865</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.41111226993865</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1.41111226993865</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1.41111226993865</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1.41111226993865</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1.41111226993865</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1.41111226993865</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>1.41111226993865</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1.41111226993865</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>1.41111226993865</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1.41111226993865</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1.41111226993865</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>1.41111226993865</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1.41111226993865</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1.41111226993865</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1.41172760736196</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1.41172760736196</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>1.41172760736196</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1.41172760736196</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>1.41172760736196</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>1.41172760736196</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>1.41172760736196</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>1.41172760736196</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>1.41172760736196</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>1.41172760736196</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>1.41172760736196</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>RUS</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1.17533435582822</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1.17533435582822</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.17533435582822</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1.17533435582822</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1.17533435582822</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1.17533435582822</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1.17533435582822</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1.17533435582822</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1.17399079754601</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1.17399079754601</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1.17399079754601</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1.17399079754601</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1.17399079754601</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>1.17399079754601</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1.17399079754601</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1.17399079754601</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1.17399079754601</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1.17399079754601</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1.17399079754601</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>1.17399079754601</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>1.17399079754601</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>1.17399079754601</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>1.17399079754601</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>1.17399079754601</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>1.17399079754601</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>1.17399079754601</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>1.17399079754601</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>SVK</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>1.3948</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>SVN</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1.42603926380368</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1.42603926380368</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.42603926380368</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1.42603926380368</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1.42603926380368</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1.42603926380368</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1.42603926380368</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1.42603926380368</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1.42603926380368</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1.42603926380368</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1.42603926380368</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1.42557300613497</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1.42557300613497</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1.42557300613497</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1.42557300613497</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1.42557300613497</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1.42557300613497</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1.42557300613497</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1.42557300613497</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1.42557300613497</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>1.42557300613497</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>1.42557300613497</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>1.42557300613497</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>1.42557300613497</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>1.42557300613497</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>1.42557300613497</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>1.42557300613497</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>SWE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1.4708</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>TUR</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>1.10857852760736</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>1.10871840490798</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>1.10871840490798</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>TWN</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>1.1297</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>USA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>1.3257</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1165,120 +6570,1470 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>WWW</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1.20020046325279</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1.20020876424189</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.2001909603105</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1.20019063478152</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1.20019065982221</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>1.20019573056216</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1.20018707900338</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>1.20018015525229</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>1.20015273569551</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>1.20016684612495</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>1.2001696882434</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>1.20016017278077</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>1.20015855765619</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>1.20015860773757</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1.20018184549894</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1.20017414548642</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1.20018670339301</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1.20016971328409</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>1.20017513459371</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>1.2001813947665</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>1.20018781770377</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>1.20020220358082</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>1.20019740828847</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>1.20018398647803</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>1.20018048078127</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>1.20018333542006</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1.2001847752598</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>HRV</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.910323926380368</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.910323926380368</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.910323926380368</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.910323926380368</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.910323926380368</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.910323926380368</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.910323926380368</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.910323926380368</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.910323926380368</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.910323926380368</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.910323926380368</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.910323926380368</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.910323926380368</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.910323926380368</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.910323926380368</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>0.910323926380368</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>0.910323926380368</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>0.910323926380368</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>0.910323926380368</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0.910630674846626</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>0.910630674846626</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>0.910630674846626</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>0.910630674846626</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>0.910630674846626</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>0.910630674846626</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>0.910630674846626</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>0.910630674846626</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>CHE</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1.10720306748466</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1.10720306748466</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.10720306748466</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>1.10718711656442</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>NOR</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1.14291840490798</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1.14291840490798</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.14291840490798</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1.14291840490798</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1.14291840490798</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>1.14291840490798</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1.14291840490798</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>1.14291840490798</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>1.14291840490798</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>1.14291840490798</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>1.14291840490798</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>1.14291840490798</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>1.14291840490798</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>1.14291840490798</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1.14291840490798</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1.14291840490798</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1.14291840490798</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1.14291840490798</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>1.14291840490798</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>1.14291840490798</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>1.14323312883436</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>1.14323312883436</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>1.14323312883436</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>1.14323312883436</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>1.14323312883436</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>1.14323312883436</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>1.14323312883436</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>ZAF</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1.15383435582822</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1.15383435582822</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.15383435582822</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1.15383435582822</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1.15383435582822</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>1.15383435582822</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1.15383435582822</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>1.15383435582822</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>1.15383435582822</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>1.15383435582822</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>1.15383435582822</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>1.15383435582822</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>1.15383435582822</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>1.15383435582822</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1.15383435582822</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1.15345705521472</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1.15345705521472</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1.15345705521472</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>1.15345705521472</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>1.15345705521472</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>1.15345705521472</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>1.15345705521472</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>1.15345705521472</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>1.15345705521472</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>1.15345705521472</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>1.15345705521472</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>1.15345705521472</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>WAS</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>1.1195</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>WAL</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1.13370490797546</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1.13370490797546</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.13370490797546</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1.13370490797546</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1.13370490797546</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1.13370490797546</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1.13370490797546</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1.13370490797546</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1.13370490797546</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1.13370490797546</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1.13384417177914</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1.13384417177914</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1.13384417177914</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1.13384417177914</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1.13384417177914</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1.13384417177914</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1.13384417177914</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1.13384417177914</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1.13384417177914</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1.13384417177914</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>1.13384417177914</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>1.13384417177914</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>1.13384417177914</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>1.13384417177914</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>1.13384417177914</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>1.13384417177914</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1.13384417177914</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>WEU</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>1.1422</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>WAF</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1.17499754601227</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1.17499754601227</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.17499754601227</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1.17499754601227</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1.17499754601227</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>1.17524601226994</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1.17524601226994</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>1.17524601226994</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>1.17524601226994</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>1.17524601226994</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>1.17524601226994</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>1.17524601226994</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>1.17524601226994</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>1.17524601226994</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1.17524601226994</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1.17524601226994</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1.17524601226994</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1.17524601226994</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>1.17524601226994</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>1.17524601226994</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>1.17524601226994</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>1.17524601226994</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>1.17524601226994</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>1.17524601226994</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>1.17524601226994</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>1.17524601226994</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>1.17524601226994</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>WME</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>1.1827</t>
         </is>
       </c>
     </row>
@@ -1320,6 +8075,11 @@
           <t>exchange.r.us</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1354,6 +8114,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
